--- a/tests/data_golden/values.expected.xlsx
+++ b/tests/data_golden/values.expected.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="45">
   <si>
     <t>values-path</t>
   </si>
@@ -147,10 +147,16 @@
     <t>${#c}</t>
   </si>
   <si>
+    <t>values-edge-space</t>
+  </si>
+  <si>
+    <t>${vspace}</t>
+  </si>
+  <si>
     <t>Alice</t>
   </si>
   <si>
-    <t>Alice Smith!</t>
+    <t xml:space="preserve">Alice Smith!</t>
   </si>
   <si>
     <t xml:space="preserve">line1
@@ -161,6 +167,9 @@
   </si>
   <si>
     <t>c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">税込　</t>
   </si>
 </sst>
 </file>
@@ -840,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -848,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -856,7 +865,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -904,7 +913,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -917,7 +926,7 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -925,7 +934,15 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1005,7 +1022,7 @@
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -1031,7 +1048,7 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -1075,7 +1092,7 @@
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1101,7 +1118,7 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
